--- a/TMP.xlsx
+++ b/TMP.xlsx
@@ -484,7 +484,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -510,7 +510,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>VPC詳細設定</t>
@@ -525,12 +525,15 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPCを選択し、詳細情報を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「お使いのVPC」を選択
+②対象VPCをクリック
+③「詳細」タブに表示される名前タグ・CIDRの画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Subnet(Public)詳細設定</t>
@@ -539,15 +542,16 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>以下のSubnet(Public)設定が設計通りになっていること
-・名前タグ
-・CIDR
-・アベイラビリティーゾーン
+・名前タグ・CIDR・アベイラビリティーゾーン
 ・Public subnet用Route Tableの付与</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; サブネットを選択し、各Subnetの詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「サブネット」を選択
+②対象のPublicサブネットをクリック
+③「詳細」タブで名前タグ・CIDR・AZ・ルートテーブルの画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -557,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Subnet(Private)詳細設定</t>
@@ -566,15 +570,16 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>以下のSubnet(Private)設定が設計通りになっていること
-・名前タグ
-・CIDR
-・アベイラビリティーゾーン
+・名前タグ・CIDR・アベイラビリティーゾーン
 ・Private subnet用Route Tableの付与</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; サブネットを選択し、各Subnetの詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「サブネット」を選択
+②対象のPrivateサブネットをクリック
+③「詳細」タブで名前タグ・CIDR・AZ・ルートテーブルの画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -583,7 +588,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>RouteTable(Public)詳細設定</t>
@@ -598,7 +603,10 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; ルートテーブルを選択し、各ルートを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「ルートテーブル」を選択
+②対象のPublicルートテーブルをクリック
+③「ルート」タブでルーティング一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -608,7 +616,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>RouteTable(Private)詳細設定</t>
@@ -623,7 +631,10 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; ルートテーブルを選択し、各ルートを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「ルートテーブル」を選択
+②対象のPrivateルートテーブルをクリック
+③「ルート」タブでルーティング一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -632,7 +643,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Network ACL設定</t>
@@ -646,12 +657,15 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; ネットワークACLを選択し、ルール内容を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「ネットワークACL」を選択
+②対象のネットワークACLをクリック
+③「インバウンドルール」「アウトバウンドルール」タブの画面をそれぞれ取得する</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8" ht="100" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>DHCPオプションセット設定</t>
@@ -664,12 +678,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; DHCPオプションセットを選択し、内容を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「DHCPオプションセット」を選択
+②対象のDHCPオプションセットをクリック
+③「詳細」タブに表示される設定内容の画面を取得する</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>VPC Endpoint(ゲートウェイ型)設定</t>
@@ -678,14 +695,16 @@
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>以下のゲートウェイ型VPC Endpoint設定が設計通りになっていること
-・名前タグ
-・サービス名
+・名前タグ・サービス名
 ・エンドポイントに各AZのPrivate subnet用Route Tableが付与</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; エンドポイントを選択し、ゲートウェイ型の詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「エンドポイント」を選択
+②対象のゲートウェイ型エンドポイントをクリック
+③「詳細」タブで名前タグ・サービス名を確認、「ルートテーブル」タブで関連付けの画面を取得する</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -694,7 +713,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="80" customHeight="1">
+    <row r="10" ht="100" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>VPC Endpoint(インターフェース型)設定</t>
@@ -703,15 +722,17 @@
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>以下のインターフェース型VPC Endpoint設定が設計通りになっていること
-・名前タグ
-・サービス名
-・全エンドポイントのサブネットに各AZのPrivate subnetが付与
-・全エンドポイントに各AZのインターフェース型VPC Endpoint用SGが付与</t>
+・名前タグ・サービス名
+・全エンドポイントに各AZのPrivate subnetが付与
+・全エンドポイントにインターフェース型VPC Endpoint用SGが付与</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; エンドポイントを選択し、インターフェース型の詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「エンドポイント」を選択
+②対象のインターフェース型エンドポイントをクリック
+③「詳細」タブで名前タグ・サービス名を確認、「サブネット」「セキュリティグループ」タブの画面をそれぞれ取得する</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -720,7 +741,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11" ht="100" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>SecurityGroup設定</t>
@@ -730,13 +751,15 @@
         <is>
           <t>Security Group設定が設計通りになっていること
 ・名前タグ
-・インバウンドで計画ルールの設定
-・アウトバウンドで計画ルールの設定</t>
+・インバウンド/アウトバウンドルールの設定</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; セキュリティグループを選択し、各SGのルールを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「セキュリティグループ」を選択
+②対象のセキュリティグループをクリック
+③「インバウンドルール」「アウトバウンドルール」タブの画面をそれぞれ取得する</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -745,7 +768,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12" ht="100" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>NAT Gateway設定</t>
@@ -754,15 +777,15 @@
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>以下のNAT Gateway設定が設計通りになっていること
-・名前タグ
-・接続タイプ
-・サブネット
-・プライマリパブリックIPv4アドレス</t>
+・名前タグ・接続タイプ・サブネット・パブリックIPv4アドレス</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; NATゲートウェイを選択し、詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「NATゲートウェイ」を選択
+②対象のNATゲートウェイをクリック
+③「詳細」タブに表示される名前タグ・接続タイプ・サブネット・IPアドレスの画面を取得する</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -771,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="80" customHeight="1">
+    <row r="13" ht="100" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Elastic IPアドレス設定</t>
@@ -785,7 +808,10 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; Elastic IPアドレスを選択し、詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「Elastic IP アドレス」を選択
+②対象のElastic IPをクリック
+③「詳細」タブに表示される名前タグ・割り当て情報の画面を取得する</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -794,7 +820,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="80" customHeight="1">
+    <row r="14" ht="100" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Internet Gateway設定</t>
@@ -808,7 +834,10 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でVPC &gt; インターネットゲートウェイを選択し、詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「VPC」&gt;「インターネットゲートウェイ」を選択
+②対象のインターネットゲートウェイをクリック
+③「詳細」タブに表示される名前タグ・VPC関連付けの画面を取得する</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -833,7 +862,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -859,7 +888,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Lambda設定確認</t>
@@ -867,19 +896,21 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>作成したLambdaが設計通りになっていること
-1. 関数名: xxxxxxxx (DB接続マスターユーザーのパスワードローテーション用)
-2. 関数名: xxxx.xxxx (RDS監視モニタリング用のロググループ(RDSOSMetrics)の存在確認用)</t>
+          <t>作成したLambda関数が設計通りになっていること
+・関数名・ランタイム</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でLambda &gt; 関数を選択し、設定タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Lambda」&gt;「関数」を選択
+②対象の関数をクリック
+③「設定」タブ&gt;「一般設定」に表示される関数名・ランタイム・メモリ・タイムアウトの画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Lambda実行ロール確認</t>
@@ -892,12 +923,15 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でLambda &gt; 関数 &gt; 設定 &gt; アクセス権限タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Lambda」&gt;「関数」を選択し対象の関数をクリック
+②「設定」タブ&gt;「アクセス権限」を選択
+③「実行ロール」に表示されるIAMロール名の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Lambda環境変数確認</t>
@@ -910,12 +944,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でLambda &gt; 関数 &gt; 設定 &gt; 環境変数タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Lambda」&gt;「関数」を選択し対象の関数をクリック
+②「設定」タブ&gt;「環境変数」を選択
+③設定されている環境変数キー一覧の画面を取得する(値はマスク可)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Lambdaトリガー確認</t>
@@ -928,12 +965,15 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でLambda &gt; 関数 &gt; トリガータブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Lambda」&gt;「関数」を選択し対象の関数をクリック
+②「設定」タブ&gt;「トリガー」を選択
+③トリガー一覧に表示されるトリガーソース・状態の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Lambda VPC設定確認</t>
@@ -941,12 +981,15 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Lambda関数のVPC設定(サブネット、SG)が設計通りになっていること</t>
+          <t>Lambda関数のVPC設定(サブネット・SG)が設計通りになっていること</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でLambda &gt; 関数 &gt; 設定 &gt; VPCタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Lambda」&gt;「関数」を選択し対象の関数をクリック
+②「設定」タブ&gt;「VPC」を選択
+③VPC・サブネット・セキュリティグループの設定画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -971,7 +1014,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -997,7 +1040,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ECRリポジトリ存在確認</t>
@@ -1010,12 +1053,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECR &gt; リポジトリを選択し、リポジトリ名を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECR(Elastic Container Registry)」&gt;「リポジトリ」を選択
+②リポジトリ一覧に表示されるリポジトリ名の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ECR暗号化確認</t>
@@ -1028,12 +1073,14 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECR &gt; リポジトリ &gt; 設定タブで暗号化設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECR」&gt;「リポジトリ」を選択し対象リポジトリをクリック
+②「設定」タブに表示される暗号化タイプの画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ECRイメージスキャン設定</t>
@@ -1046,7 +1093,9 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECR &gt; リポジトリ &gt; 設定タブでイメージスキャン設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECR」&gt;「リポジトリ」を選択し対象リポジトリをクリック
+②「設定」タブ内「イメージスキャン」セクションの設定内容の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1055,7 +1104,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ECRライフサイクルポリシー設定</t>
@@ -1068,7 +1117,9 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECR &gt; リポジトリ &gt; ライフサイクルポリシータブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECR」&gt;「リポジトリ」を選択し対象リポジトリをクリック
+②「ライフサイクルポリシー」タブに表示されるポリシー内容の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1093,7 +1144,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1119,7 +1170,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>イベントバス設定確認</t>
@@ -1128,13 +1179,15 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>EventBridgeのイベントバスが設計通りに作成されていること
-・名前
-・タイプ</t>
+・名前・タイプ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEventBridge &gt; イベントバスを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EventBridge」&gt;「イベントバス」を選択
+②対象のイベントバスをクリック
+③「詳細」画面に表示される名前・タイプの画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1143,7 +1196,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ルール設定確認</t>
@@ -1152,19 +1205,20 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>EventBridgeルールが設計通りに設定されていること
-・ルール名
-・イベントバス名
-・状態(有効)</t>
+・ルール名・イベントバス名・状態(有効)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEventBridge &gt; ルールを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EventBridge」&gt;「ルール」を選択
+②対象のルールをクリック
+③「詳細」画面に表示されるルール名・イベントバス・状態の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ルールのイベントパターン/スケジュール確認</t>
@@ -1177,7 +1231,9 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEventBridge &gt; ルールを選択し、イベントパターンまたはスケジュールタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EventBridge」&gt;「ルール」を選択し対象ルールをクリック
+②「イベントパターン」または「スケジュール式」セクションに表示される設定内容の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1186,7 +1242,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ルールのターゲット確認</t>
@@ -1199,12 +1255,14 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEventBridge &gt; ルール &gt; ターゲットタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EventBridge」&gt;「ルール」を選択し対象ルールをクリック
+②「ターゲット」セクションに表示されるターゲット一覧(ターゲットタイプ・ARN等)の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ルール実行IAMロール確認</t>
@@ -1212,13 +1270,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EventBridgeルールに設定されたIAMロールが設計通りになっていること
-・ターゲットへの実行権限が付与されていること</t>
+          <t>EventBridgeルールに設定されたIAMロールが設計通りになっていること</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEventBridge &gt; ルール &gt; ターゲットタブでIAMロールを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EventBridge」&gt;「ルール」を選択し対象ルールをクリック
+②「ターゲット」セクション内の各ターゲットに表示されるIAMロール欄の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1243,7 +1302,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1269,7 +1328,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>EC2アラーム設定確認</t>
@@ -1278,21 +1337,21 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>EC2インスタンスのCloudWatchアラームが設計通りに設定されていること
-・StatusCheckFailed_System: 0
-・StatusCheckFailed_Instance: 0
-・CPUUtilization: 80%
-・mem_used_percent: 80%
-・disk_used_percent: 80%</t>
+・StatusCheckFailed_System/Instance・CPUUtilization
+・mem_used_percent・disk_used_percent</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、EC2関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②EC2関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間・アクション(通知先)の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ECS(Fargate)アラーム設定確認</t>
@@ -1301,19 +1360,20 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>ECS(Fargate)クラスターのCloudWatchアラームが設計通りに設定されていること
-・CPUUtilization: 80%
-・MemoryUtilization: 80%
-・TaskCount: 1未満</t>
+・CPUUtilization・MemoryUtilization・TaskCount</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、ECS関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②ECS関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間・アクション(通知先)の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>RDSアラーム設定確認</t>
@@ -1323,23 +1383,22 @@
         <is>
           <t>RDSインスタンスのCloudWatchアラームが設計通りに設定されていること
 [5回連続]
-・CPUUtilization: 80%以上
-・Deadlocks: 1件超
-・WriteLatency: 100ms以上
-・ReadLatency: 100ms以上
-・FreeableMemory: 1GB以下
-・FreeLocalStorage: 1GB以下
-・FreeStorageSpace: 1GB以下</t>
+・CPUUtilization・Deadlocks
+・WriteLatency・ReadLatency
+・FreeableMemory・FreeLocalStorage・FreeStorageSpace</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、RDS関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②RDS関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間・アクション(通知先)の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Auroraアラーム設定確認</t>
@@ -1349,19 +1408,20 @@
         <is>
           <t>AuroraのCloudWatchアラームが設計通りに設定されていること
 [1回連続]
-・AuroraReplicaLag: 1,000ms以上
-・AuroraVolumeBytesLeftTotal: 10TB以下
-・VolumeBytesUsed: 118TB以上</t>
+・AuroraReplicaLag・AuroraVolumeBytesLeftTotal・VolumeBytesUsed</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、Aurora関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②Aurora関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間・アクション(通知先)の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>アラーム通知先設定確認</t>
@@ -1374,7 +1434,9 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラーム &gt; 対象アラームを選択し、通知設定(アクション)を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択し対象アラームをクリック
+②「詳細」タブ&gt;「アクション」セクションに表示されるSNSトピックARN・通知条件の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1399,7 +1461,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1425,7 +1487,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Log Group設定確認</t>
@@ -1434,18 +1496,20 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>CloudWatch Logが仕様通りの設定で構築されていること
-・名前
-・保持期間: 365日</t>
+・名前・保持期間: 365日</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; ロググループを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「ロググループ」を選択
+②対象のロググループをクリック
+③「詳細」画面に表示されるロググループ名・保持設定の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ロググループ名称確認</t>
@@ -1458,12 +1522,14 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; ロググループ一覧で名前を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「ロগগループ」を選択
+②ロググループ一覧に表示される名前の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>メトリクスフィルター設定確認</t>
@@ -1476,7 +1542,9 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; ロググループ &gt; メトリクスフィルタータブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「ロググループ」を選択し対象ロググループをクリック
+②「メトリクスフィルター」タブに表示されるフィルターパターン・メトリクス名の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1501,7 +1569,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1527,7 +1595,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SNSトピック設定確認</t>
@@ -1540,12 +1608,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSNS &gt; トピックを選択し、名前を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SNS(Simple Notification Service)」&gt;「トピック」を選択
+②トピック一覧に表示されるトピック名の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>SNSサブスクリプション確認</t>
@@ -1554,14 +1624,14 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>SNSトピックのサブスクリプション(通知先)が設計通りに設定されていること
-・プロトコル(Email等)
-・エンドポイント(メールアドレス等)
-・ステータス: 確認済み</t>
+・プロトコル・エンドポイント・ステータス: 確認済み</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSNS &gt; トピック &gt; サブスクリプションタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SNS」&gt;「トピック」を選択し対象トピックをクリック
+②「サブスクリプション」セクションに表示されるプロトコル・エンドポイント・ステータスの画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1570,7 +1640,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SNSアクセスポリシー確認</t>
@@ -1583,7 +1653,9 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSNS &gt; トピック &gt; アクセスポリシータブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SNS」&gt;「トピック」を選択し対象トピックをクリック
+②「アクセスポリシー」セクションに表示されるポリシー内容の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1592,7 +1664,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>SNS暗号化設定確認</t>
@@ -1605,7 +1677,9 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSNS &gt; トピック &gt; 暗号化タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SNS」&gt;「トピック」を選択し対象トピックをクリック
+②「暗号化」セクションに表示されるSSE設定の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
@@ -1626,7 +1700,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1652,7 +1726,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SES送信ドメイン確認</t>
@@ -1665,7 +1739,10 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSES &gt; 検証済みID &gt; ドメインを選択し、検証ステータスを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SES(Simple Email Service)」&gt;「検証済みID」を選択
+②対象のドメインをクリック
+③「詳細」画面に表示されるIDステータス(検証済み)の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1674,7 +1751,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>SES DKIM設定確認</t>
@@ -1687,7 +1764,9 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSES &gt; 検証済みID &gt; DKIMタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SES」&gt;「検証済みID」を選択し対象ドメインをクリック
+②「DKIM」タブに表示されるDKIM設定ステータス(「成功」)の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1696,7 +1775,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SES本番環境(サンドボックス外)確認</t>
@@ -1709,7 +1788,9 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSES &gt; アカウントダッシュボードで送信制限を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SES」&gt;「アカウントダッシュボード」を選択
+②「送信制限」セクションに表示される「本番稼働へのアクセス」状態の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1718,7 +1799,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>SES設定セット確認</t>
@@ -1727,13 +1808,15 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>SESの設定セットが設計通りに設定されていること
-・設定セット名
-・イベント送信先</t>
+・設定セット名・イベント送信先</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSES &gt; 設定セットを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SES」&gt;「設定セット」を選択
+②対象の設定セットをクリック
+③「イベント送信先」タブに表示される送信先の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1742,7 +1825,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SES送信元メールアドレス検証</t>
@@ -1755,7 +1838,9 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSES &gt; 検証済みID &gt; メールアドレスを選択し、ステータスを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SES」&gt;「検証済みID」を選択
+②メールアドレス一覧に表示されるIDステータス(検証済み)の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -1776,7 +1861,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1802,7 +1887,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>WAF ACL名設定確認</t>
@@ -1815,12 +1900,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でWAF &gt; Web ACLを選択し、名前を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「WAF &amp; Shield」&gt;「Web ACL」を選択
+②Web ACL一覧に表示される名前の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>WAFルールとデフォルトアクション確認</t>
@@ -1834,18 +1921,19 @@
 ・AWSManagedRulesKnownBadInputsRuleSet
 ・AWSManagedRulesBotControlRuleSet
 ・AWSManagedRulesAnonymousIpList
-【アクション】
-・Allow</t>
+【アクション】Allow</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でWAF &gt; Web ACL &gt; ルールタブを選択し、ルール一覧と各アクションを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「WAF &amp; Shield」&gt;「Web ACL」を選択し対象Web ACLをクリック
+②「ルール」タブに表示されるルール一覧・各アクション・デフォルトウェブACLアクションの画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>WAFと対象リソースの関連付け確認</t>
@@ -1858,12 +1946,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でWAF &gt; Web ACL &gt; 関連付けられたAWSリソースタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「WAF &amp; Shield」&gt;「Web ACL」を選択し対象Web ACLをクリック
+②「関連付けられているAWSリソース」タブに表示されるリソース名・ARNの画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>WAFログ設定確認</t>
@@ -1876,7 +1966,9 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でWAF &gt; Web ACL &gt; ログ記録とメトリクスタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「WAF &amp; Shield」&gt;「Web ACL」を選択し対象Web ACLをクリック
+②「ログ記録とメトリクス」タブに表示されるログ記録先(CloudWatch Logs等)の設定画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1901,7 +1993,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1927,7 +2019,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>API Gateway種別確認</t>
@@ -1940,7 +2032,9 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でAPI Gateway &gt; APIを選択し、種別を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「API Gateway」を選択
+②API一覧に表示されるAPI名・タイプ(REST API)の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1950,7 +2044,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>エンドポイントタイプ確認</t>
@@ -1963,7 +2057,10 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でAPI Gateway &gt; API &gt; 設定タブでエンドポイントタイプを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「API Gateway」を選択し対象APIをクリック
+②左サイドメニュー「設定」を選択
+③「エンドポイントタイプ」に表示される「プライベート」設定の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1973,7 +2070,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>APIリソース/メソッド設定確認</t>
@@ -1986,12 +2083,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でAPI Gateway &gt; API &gt; リソースを選択し、各メソッドの統合設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「API Gateway」を選択し対象APIをクリック
+②左サイドメニュー「リソース」を選択
+③リソースツリーと各メソッドの統合タイプ・統合先の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>APIステージ設定確認</t>
@@ -2000,18 +2100,20 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>APIステージが設計通りに設定されていること
-・ステージ名
-・デプロイ済み</t>
+・ステージ名・デプロイ済み</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でAPI Gateway &gt; API &gt; ステージを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「API Gateway」を選択し対象APIをクリック
+②左サイドメニュー「ステージ」を選択
+③ステージ一覧に表示されるステージ名・デプロイ日時の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>カスタムドメイン設定確認</t>
@@ -2024,7 +2126,10 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でAPI Gateway &gt; カスタムドメイン名を選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「API Gateway」&gt;「カスタムドメイン名」を選択
+②対象のカスタムドメインをクリック
+③「詳細」画面に表示されるドメイン名・ACM証明書・APIマッピングの画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2033,7 +2138,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>APIリソースポリシー確認</t>
@@ -2047,7 +2152,10 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でAPI Gateway &gt; API &gt; リソースポリシータブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「API Gateway」を選択し対象APIをクリック
+②左サイドメニュー「リソースポリシー」を選択
+③表示されているポリシーJSON内容の画面を取得する</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -2072,7 +2180,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2098,7 +2206,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SageMaker環境設定確認</t>
@@ -2107,18 +2215,20 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SageMakerの機械学習環境が設計通りに設定されていること
-・環境タイプ(Notebook Instance または SageMaker Studio)
-・インスタンスタイプ(ml.t3.medium / ml.m5.xlarge等)</t>
+・環境タイプ・インスタンスタイプ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSageMaker &gt; ノートブックインスタンスまたはSageMaker Studio &gt; ドメインを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SageMaker」&gt;「ノートブックインスタンス」または「Studio」を選択
+②対象のインスタンス/ドメインをクリック
+③「詳細」画面に表示されるインスタンスタイプ・ステータスの画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>SageMakerアクセス元設定確認</t>
@@ -2131,7 +2241,9 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSageMaker &gt; ノートブックインスタンス &gt; ネットワーク設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SageMaker」&gt;「ノートブックインスタンス」を選択し対象インスタンスをクリック
+②「詳細」画面内「ネットワーク」セクションに表示されるVPC・サブネット・セキュリティグループの画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -2140,7 +2252,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SageMaker自動停止設定確認</t>
@@ -2148,12 +2260,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>一定時間アイドル後に自動停止が設定されていること(推奨:有効)</t>
+          <t>一定時間アイドル後に自動停止が設定されていること(推奨: 有効)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSageMaker &gt; ノートブックインスタンス &gt; 設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SageMaker」&gt;「ノートブックインスタンス」を選択し対象インスタンスをクリック
+②「詳細」画面内「インスタンスの設定」セクションに表示されるアイドル状態でのシャットダウン設定の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2162,7 +2276,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>SageMaker暗号化設定確認</t>
@@ -2175,7 +2289,9 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSageMaker &gt; ノートブックインスタンス &gt; 設定 &gt; 暗号化キーを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SageMaker」&gt;「ノートブックインスタンス」を選択し対象インスタンスをクリック
+②「詳細」画面内「暗号化キー」に表示されるKMSキーARNの画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2184,7 +2300,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SageMaker IAMロール確認</t>
@@ -2197,7 +2313,9 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSageMaker &gt; ノートブックインスタンス &gt; アクセス許可を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「SageMaker」&gt;「ノートブックインスタンス」を選択し対象インスタンスをクリック
+②「詳細」画面内「アクセス許可と暗号化」セクションに表示されるIAMロール名の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -2218,7 +2336,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2244,7 +2362,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ドメイン名設定</t>
@@ -2257,12 +2375,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRoute53 &gt; ホストゾーンを選択し、ドメイン名を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Route 53」&gt;「ホストゾーン」を選択
+②ホストゾーン一覧に表示されるドメイン名の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ホストゾーン設定</t>
@@ -2271,19 +2391,21 @@
       <c r="B3" s="3" t="inlineStr">
         <is>
           <t>ホストゾーンが設計通りに作成されていること
-・ホストゾーン名
-・タイプ(パブリック/プライベート)
+・ホストゾーン名・タイプ(パブリック/プライベート)
 ・VPC関連付け(プライベートの場合)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRoute53 &gt; ホストゾーンを選択し、設定詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Route 53」&gt;「ホストゾーン」を選択
+②対象のホストゾーンをクリック
+③「詳細」セクションに表示されるタイプ・VPC関連付けの画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>レコードセット設定</t>
@@ -2292,14 +2414,15 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>DNSレコードが設計通りに設定されていること
-・レコード名
-・タイプ(A/CNAME/ALIAS等)
-・値/ルーティング先</t>
+・レコード名・タイプ(A/CNAME/ALIAS等)・値/ルーティング先</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRoute53 &gt; ホストゾーン &gt; レコードを選択し、各レコードの内容を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Route 53」&gt;「ホストゾーン」を選択
+②対象のホストゾーンをクリック
+③「レコード」一覧に表示されるレコード名・タイプ・値の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2308,7 +2431,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ヘルスチェック設定</t>
@@ -2317,14 +2440,15 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>ヘルスチェックが設計通りに設定されていること
-・プロトコル
-・エンドポイント
-・間隔</t>
+・プロトコル・エンドポイント・間隔</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRoute53 &gt; ヘルスチェックを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Route 53」&gt;「ヘルスチェック」を選択
+②対象のヘルスチェックをクリック
+③「詳細」タブに表示されるプロトコル・エンドポイント・間隔の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2349,7 +2473,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2375,7 +2499,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ALB詳細設定</t>
@@ -2384,19 +2508,20 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>ALBが仕様通りの設定で構築されていること
-・名前タグ(dtds-prd-alb)
-・種類(Application Load Balancer)
-・リスナー(HTTPS)</t>
+・名前タグ・種類・リスナー</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ロードバランサーを選択し、詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ロードバランサー」を選択
+②対象のALBをクリック
+③「詳細」タブに表示される名前・タイプ・状態の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ALBデプロイサブネット確認</t>
@@ -2411,12 +2536,15 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ロードバランサーを選択し、アベイラビリティーゾーンを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ロードバランサー」を選択
+②対象のALBをクリック
+③「詳細」タブ内「ネットワークマッピング」セクションでAZ・サブネット一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ALBセキュリティグループ確認</t>
@@ -2430,12 +2558,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ロードバランサー &gt; セキュリティタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ロードバランサー」を選択
+②対象のALBをクリック
+③「セキュリティ」タブに表示されるセキュリティグループ一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ALB属性設定</t>
@@ -2448,12 +2579,15 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ロードバランサー &gt; 属性タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ロードバランサー」を選択
+②対象のALBをクリック
+③「属性」タブに表示される設定内容の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ALBリスナールール設定(デフォルト)</t>
@@ -2463,19 +2597,21 @@
         <is>
           <t>ALBのリスナールールが要求仕様通りの設定で展開されていること
 ・条件(IF): 他のルールが適用されない場合
-・アクション: ターゲットグループへの転送
-  dtds-prd-alb-tg:1(100%)
-  ターゲットグループの維持:オフ</t>
+・アクション: ターゲットグループへの転送</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ロードバランサー &gt; リスナータブ &gt; ルールを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ロードバランサー」を選択
+②対象のALBをクリック
+③「リスナーとルール」タブで対象リスナーをクリック
+④ルール一覧画面(デフォルトルールの条件・アクション)を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>ALBターゲットグループ詳細設定</t>
@@ -2484,22 +2620,21 @@
       <c r="B7" s="3" t="inlineStr">
         <is>
           <t>ターゲットグループの詳細設定が設計通りになっていること
-・ターゲットの種類: instance
-・プロトコル/ポート: HTTP:80
-・プロトコルバージョン: HTTP1(デフォルト)
-・VPC: AWS-apnortheast1-DTDS-official-site-PRD-PRD-VPC-01
-・IPアドレスタイプ: IPv4
-・ロードバランサー: 構築したALB</t>
+・ターゲットの種類・プロトコル/ポート・プロトコルバージョン
+・VPC・IPアドレスタイプ・ロードバランサー</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ターゲットグループを選択し、詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ターゲットグループ」を選択
+②対象のターゲットグループをクリック
+③「詳細」タブに表示されるターゲット種類・プロトコル・ポート等の画面を取得する</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8" ht="100" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>ALBターゲットグループ属性設定</t>
@@ -2512,12 +2647,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ターゲットグループ &gt; 属性タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ターゲットグループ」を選択
+②対象のターゲットグループをクリック
+③「属性」タブに表示される設定内容の画面を取得する</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>ALBリスナーTLS設定</t>
@@ -2530,7 +2668,10 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ロードバランサー &gt; リスナータブを選択し、HTTPS設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ロードバランサー」を選択
+②対象のALBをクリック
+③「リスナーとルール」タブに表示されるプロトコル・ポート・TLSバージョンの画面を取得する</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2539,7 +2680,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="80" customHeight="1">
+    <row r="10" ht="100" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ALBヘルスチェック設定</t>
@@ -2548,15 +2689,16 @@
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>ヘルスチェックがデフォルト設定通りになっていること
-・プロトコル: HTTP
-・パス: /
-・タイムアウト: 10秒
-・間隔: 30秒</t>
+・プロトコル: HTTP・パス: /
+・タイムアウト: 10秒・間隔: 30秒</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; ターゲットグループ &gt; ヘルスチェックタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「ターゲットグループ」を選択
+②対象のターゲットグループをクリック
+③「ヘルスチェック」タブに表示されるプロトコル・パス・タイムアウト・間隔の画面を取得する</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -2577,7 +2719,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2603,7 +2745,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>EC2スペック確認</t>
@@ -2612,23 +2754,21 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>EC2が要求仕様通りの設定で構築されていること
-・名前タグ
-・OS
-・InstanceType
-・Storage(GB)
-・EBS暗号化(enable)
-・AZ
-・Subnet(PrivateSubnet/CIDR)</t>
+・名前タグ・OS・InstanceType・Storage・EBS暗号化・AZ・Subnet</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でEC2 &gt; インスタンスを選択し、詳細タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「EC2」&gt;「インスタンス」を選択
+②対象のインスタンスをクリック
+③「詳細」タブに表示されるインスタンスタイプ・AMI・サブネット・AZ等の画面を取得する
+④「ストレージ」タブでEBSボリュームの暗号化状態の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>EC2インスタンスモニタリングアラーム</t>
@@ -2638,17 +2778,17 @@
         <is>
           <t>以下のCloudWatchアラームが設計通りに設定されていること
 [3分間監視]
-・CPU使用量(CPUUtilization &gt;= 80%)
-・メモリ使用量(mem_used_percent &gt;= 80%)
-・ディスク使用量(disk_used_percent &gt;= 80%)
+・CPUUtilization &gt;= 80%・mem_used_percent &gt;= 80%・disk_used_percent &gt;= 80%
 [10分間監視]
-・StatusCheckFailed_Instance &gt; 0(10データポイント)
-・StatusCheckFailed_System &gt; 0(10データポイント)</t>
+・StatusCheckFailed_Instance &gt; 0・StatusCheckFailed_System &gt; 0</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、EC2関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②EC2関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -2657,7 +2797,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>バックアッププラン確認</t>
@@ -2666,20 +2806,22 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>以下の通りバックアッププランが設定されていること
-・頻度: 毎日
-・スケジュール: C#チーム設定
-・保管世代数: 30日(デフォルト)
+・頻度: 毎日・保管世代数: 30日(デフォルト)
 ・バックアップ対象タグ設定</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でAWS Backup &gt; バックアッププランを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「AWS Backup」&gt;「バックアッププラン」を選択
+②対象のバックアッププランをクリック
+③「バックアップルール」セクションでスケジュール・保持期間の画面を取得する
+④「リソースの割り当て」タブでタグ設定の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>ミドルウェアインストール確認</t>
@@ -2688,28 +2830,22 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>以下のミドルウェアがインストールされ、正常に起動していること
-・Qualys Cloud Agent
-・Microsoft Defender for Endpoint(MDE)
-・Splunk Agent
-・BigFix
-・SSM Agent
-・CloudWatch Agent
-・CodeDeploy Agent
-・Ruby</t>
+・Qualys Cloud Agent・MDE・Splunk Agent
+・BigFix・SSM Agent・CloudWatch Agent
+・CodeDeploy Agent・Ruby</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>サーバにSSH/SSM接続後、Shell Script(IPCMS_EngineeringSection_UnitTest.sh)を実行
+          <t>対象EC2にSSHまたはSSM Session Manager接続後、以下コマンドを実行し出力結果の画面を取得する
 # Qualys Cloud Agent
 sudo systemctl status qualys-cloud-agent
-sudo systemctl is-enabled qualys-cloud-agent
 # MDE
 mdatp health
 # Splunk Agent
 sudo /opt/splunkforwarder/bin/splunk version
 # BigFix
-sudo grep "Client version" /var/opt/BESClient/_BESData/__Global/Logs/[日付].log
+sudo grep 'Client version' /var/opt/BESClient/_BESData/__Global/Logs/[日付].log
 # SSM Agent
 systemctl status amazon-ssm-agent
 # CloudWatch Agent
@@ -2738,7 +2874,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2764,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>証明書設定確認</t>
@@ -2773,18 +2909,20 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>証明書の以下の設定が設計通りになっていること
-・名前タグ
-・ドメイン名</t>
+・名前タグ・ドメイン名</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でACM &gt; 証明書を選択し、詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Certificate Manager(ACM)」を選択
+②対象の証明書をクリック
+③「詳細」画面に表示されるドメイン名・名前タグの画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>証明書ステータス確認</t>
@@ -2797,15 +2935,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でACM &gt; 証明書一覧でステータスを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Certificate Manager(ACM)」を選択
+②証明書一覧に表示されるステータス列の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>証明書有効期限確認</t>
+          <t>証明書有効期限・自動更新確認</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -2816,7 +2956,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でACM &gt; 証明書の詳細で有効期限と自動更新設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Certificate Manager(ACM)」を選択
+②対象の証明書をクリック
+③「詳細」画面に表示される有効期限・更新の適格性の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2841,7 +2984,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2867,7 +3010,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Fargateスペック確認</t>
@@ -2876,22 +3019,22 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>ECS Fargateが要求仕様通りの設定で構築されていること
-・クラスタ名
-・サービス名
-・タスク定義
-・1タスクあたりのスペック
-  CPU: xxxx(vCPU)
-  メモリ: xxx MiB(x GB)</t>
+・クラスタ名・サービス名・タスク定義
+・CPU/メモリのスペック</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECS &gt; クラスター &gt; サービスを選択し、タスク定義の詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECS」&gt;「クラスター」を選択し、対象クラスターをクリック
+②「サービス」タブで対象サービスをクリック
+③「設定とネットワーク」タブに表示されるタスク定義・CPUアーキテクチャの画面を取得する
+④左メニュー「ECS」&gt;「タスク定義」で対象タスク定義をクリックしCPU・メモリの画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Fargateデプロイサブネット確認</t>
@@ -2904,7 +3047,10 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECS &gt; クラスター &gt; サービス &gt; タスクを選択し、ネットワーク設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECS」&gt;「クラスター」を選択し、対象クラスターをクリック
+②「サービス」タブで対象サービスをクリック
+③「設定とネットワーク」タブ内「ネットワーク設定」セクションのサブネット一覧画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -2913,7 +3059,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>FargateセキュリティグループATTACH確認</t>
@@ -2926,7 +3072,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECS &gt; クラスター &gt; サービス &gt; タスクを選択し、セキュリティグループを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECS」&gt;「クラスター」を選択し、対象クラスターをクリック
+②「サービス」タブで対象サービスをクリック
+③「設定とネットワーク」タブ内「ネットワーク設定」セクションのセキュリティグループ一覧画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2935,7 +3084,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Fargateオートスケーリング設定</t>
@@ -2944,16 +3093,15 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>FargateのAutoScaling設定が仕様通りになっていること
-・最小タスク数
-・最大タスク数
-・スケーリングポリシー
-  CPU使用率: 80%以上
-  メモリ使用率: 80%以上</t>
+・最小/最大タスク数・スケーリングポリシー(CPU/メモリ80%)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でECS &gt; クラスター &gt; サービス &gt; オートスケーリングタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「ECS」&gt;「クラスター」を選択し、対象クラスターをクリック
+②「サービス」タブで対象サービスをクリック
+③「スケーリング」タブに表示される最小・最大タスク数およびポリシー一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2962,7 +3110,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ECSタスクモニタリングアラーム</t>
@@ -2971,15 +3119,17 @@
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>以下のCloudWatchアラームが設計通りに設定されていること
-[3分間監視]
-・CPUUtilization(平均80%以上でアラート)
-・MemoryUtilization(平均80%以上でアラート)
+・CPUUtilization(平均80%以上)
+・MemoryUtilization(平均80%以上)
 ・TaskCount(0個になるとアラート)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、ECS関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②ECS関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3004,7 +3154,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3030,7 +3180,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>RDSインスタンス詳細設定</t>
@@ -3039,22 +3189,22 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>RDSインスタンスが要求仕様通りの設定で構築されていること
-・名前タグ
-・DBエンジン/バージョン
-・インスタンスタイプ
-・ストレージ
-・Multi-AZ構成
-・DBサブネットグループ</t>
+・名前タグ・DBエンジン/バージョン・インスタンスタイプ
+・ストレージ・Multi-AZ・DBサブネットグループ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベースを選択し、設定タブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択
+②対象のDBインスタンスをクリック
+③「設定」タブに表示されるエンジン・インスタンスクラス・ストレージ等の画面を取得する
+④「接続とセキュリティ」タブでMulti-AZ・サブネットグループの画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>RDSサブネットグループ確認</t>
@@ -3062,18 +3212,20 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>仕様通りのサブネットにRDSがデプロイされていること
-・DBサブネットグループ名</t>
+          <t>仕様通りのサブネットにRDSがデプロイされていること</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; サブネットグループを選択し、含まれるサブネットを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「サブネットグループ」を選択
+②対象のサブネットグループをクリック
+③「詳細」画面に表示されるサブネット一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>RDSセキュリティグループ確認</t>
@@ -3086,12 +3238,15 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベース &gt; 接続とセキュリティタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択
+②対象のDBインスタンスをクリック
+③「接続とセキュリティ」タブ内「セキュリティグループ」欄の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>RDSバックアップ設定</t>
@@ -3104,12 +3259,15 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベース &gt; メンテナンスとバックアップタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択
+②対象のDBインスタンスをクリック
+③「メンテナンスとバックアップ」タブ内「バックアップ保持期間」の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>RDSメンテナンス/バックアップ時間帯</t>
@@ -3124,7 +3282,10 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベース &gt; メンテナンスとバックアップタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択
+②対象のDBインスタンスをクリック
+③「メンテナンスとバックアップ」タブ内「バックアップウィンドウ」「メンテナンスウィンドウ」の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3133,7 +3294,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>RDS Multi-AZ設定</t>
@@ -3146,7 +3307,10 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベース &gt; 設定タブで確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択
+②対象のDBインスタンスをクリック
+③「設定」タブ内「Multi-AZ」欄の画面を取得する</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3156,7 +3320,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8" ht="100" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RDSパラメータグループ設定</t>
@@ -3169,12 +3333,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; パラメータグループを選択し、各パラメータを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「パラメータグループ」を選択
+②対象のパラメータグループをクリック
+③「パラメータ」タブに表示されるパラメータ一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>RDSパスワードローテーション設定</t>
@@ -3188,17 +3355,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSecrets Manager &gt; シークレットを選択し、ローテーション設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Secrets Manager」&gt;「シークレット」を選択
+②RDS用のシークレットをクリック
+③「ローテーション設定」セクションに表示されるローテーション間隔の画面を取得する</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Secrets Managerと連携していること
-情報セキュリティ管理ルールに則り30日以内でのローテーションが必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
+          <t>情報セキュリティ管理ルールに則り30日以内でのローテーションが必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RDSモニタリングアラーム</t>
@@ -3208,18 +3377,17 @@
         <is>
           <t>以下のCloudWatchアラームが設計通りに設定されていること
 [5回連続]
-・CPUUtilization: 80%以上
-・Deadlocks: 1件超
-・WriteLatency: 100ms以上
-・ReadLatency: 100ms以上
-・FreeableMemory: 1GB以下
-・FreeLocalStorage: 1GB以下
-・FreeStorageSpace: 1GB以下</t>
+・CPUUtilization: 80%以上・Deadlocks: 1件超
+・WriteLatency/ReadLatency: 100ms以上
+・FreeableMemory/FreeLocalStorage/FreeStorageSpace: 1GB以下</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、RDS関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②RDS関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間の画面を取得する</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3228,7 +3396,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11" ht="100" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>RDSイベントサブスクリプション(インスタンス)</t>
@@ -3237,19 +3405,20 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>イベントサブスクリプションが設計通りになっていること
-・ソースタイプ: インスタンス
-・イベントカテゴリ: すべて
-・有効: ON</t>
+・ソースタイプ: インスタンス・イベントカテゴリ: すべて・有効: ON</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; イベントサブスクリプションを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「イベントサブスクリプション」を選択
+②対象のサブスクリプション(インスタンス)をクリック
+③「詳細」画面に表示されるソースタイプ・カテゴリ・有効状態の画面を取得する</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12" ht="100" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RDSイベントサブスクリプション(クラスター)</t>
@@ -3258,14 +3427,15 @@
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>イベントサブスクリプションが設計通りになっていること
-・ソースタイプ: クラスター
-・イベントカテゴリ: すべて
-・有効: ON</t>
+・ソースタイプ: クラスター・イベントカテゴリ: すべて・有効: ON</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; イベントサブスクリプションを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「イベントサブスクリプション」を選択
+②対象のサブスクリプション(クラスター)をクリック
+③「詳細」画面に表示されるソースタイプ・カテゴリ・有効状態の画面を取得する</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -3286,7 +3456,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3312,7 +3482,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Auroraデプロイサブネット確認</t>
@@ -3320,18 +3490,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>仕様通りのサブネットにAuroraがデプロイされていること
-・サブネットグループ名</t>
+          <t>仕様通りのサブネットにAuroraがデプロイされていること</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; サブネットグループを選択し、Auroraクラスターのサブネットを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「サブネットグループ」を選択
+②AuroraクラスターのDBサブネットグループをクリック
+③「詳細」画面に表示されるサブネット一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>AuroraセキュリティグループATTACH確認</t>
@@ -3344,12 +3516,15 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベース &gt; 接続とセキュリティタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択し、対象Auroraクラスターをクリック
+②Writerインスタンスをクリック
+③「接続とセキュリティ」タブ内「セキュリティグループ」欄の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Auroraスペック確認</t>
@@ -3358,23 +3533,27 @@
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Auroraが要求仕様通りの設定で構築されていること
-①[クラスター] Identifier
-②[DBクラスターパラメータグループ]
-③[インスタンス] Engine/Engine Version/InstanceType/Multi-AZ/DBMasterUserName/DatabaseName/DeletionProtection/Subnet
-④[DBインスタンスパラメータグループ]
-⑤[メンテナンス、ロギング]
-⑥[バックアップ] Backup保持期間
-⑦[クロスリージョンレプリケーター]</t>
+①クラスター識別子
+②DBクラスターパラメータグループ
+③インスタンス設定(Engine/バージョン/InstanceType/Multi-AZ等)
+④DBインスタンスパラメータグループ
+⑤メンテナンス・ロギング
+⑥バックアップ保持期間
+⑦クロスリージョンレプリケーター</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベースを選択し、クラスター/インスタンス詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択し、対象Auroraクラスターをクリック
+②「設定」タブで識別子・パラメータグループ・Multi-AZの画面を取得する
+③各インスタンスをクリックし、「設定」タブでエンジン・インスタンスクラスの画面を取得する
+④「メンテナンスとバックアップ」タブでバックアップ保持期間の画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="100" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Auroraパラメータグループ設定</t>
@@ -3382,17 +3561,20 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>DBクラスターパラメータグループ・DBインスタンスパラメータグループの設定内容がデフォルト値と同一になっていること</t>
+          <t>DBクラスター/インスタンスパラメータグループの設定内容がデフォルト値と同一になっていること</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; パラメータグループを選択し、各パラメータを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「パラメータグループ」を選択
+②クラスター用・インスタンス用それぞれのパラメータグループをクリック
+③「パラメータ」タブに表示される設定値一覧の画面を取得する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="100" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Auroraバックアップ設定</t>
@@ -3405,7 +3587,9 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベース &gt; メンテナンスとバックアップタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択し、対象Auroraクラスターをクリック
+②「メンテナンスとバックアップ」タブ内「バックアップ保持期間」の画面を取得する</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3414,7 +3598,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7" ht="100" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Auroraメンテナンス/バックアップ時間帯</t>
@@ -3429,12 +3613,14 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベース &gt; メンテナンスとバックアップタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択し、対象Auroraクラスターをクリック
+②「メンテナンスとバックアップ」タブ内「バックアップウィンドウ」「メンテナンスウィンドウ」の画面を取得する</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8" ht="100" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Auroraリードレプリカ構成確認</t>
@@ -3447,7 +3633,9 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; データベースを選択し、クラスター内のインスタンス構成を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「データベース」を選択し、対象Auroraクラスターをクリック
+②クラスター内のインスタンス一覧(Writer/Reader)の画面を取得する</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3458,10 +3646,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>AuroraモニタリングアラームS</t>
+          <t>Auroraモニタリングアラーム</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3475,7 +3663,10 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でCloudWatch &gt; アラームを選択し、Aurora関連アラームの設定値を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「CloudWatch」&gt;「アラーム」&gt;「すべてのアラーム」を選択
+②Aurora関連の各アラームをクリック
+③「詳細」タブに表示されるメトリクス名・閾値・評価期間の画面を取得する</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -3484,7 +3675,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="80" customHeight="1">
+    <row r="10" ht="100" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RDSイベントサブスクリプション(インスタンス)</t>
@@ -3493,19 +3684,20 @@
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>イベントサブスクリプションが設計通りになっていること
-・ソースタイプ: インスタンス
-・イベントカテゴリ: すべて
-・有効: ON</t>
+・ソースタイプ: インスタンス・イベントカテゴリ: すべて・有効: ON</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; イベントサブスクリプションを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「イベントサブスクリプション」を選択
+②対象のサブスクリプション(インスタンス)をクリック
+③「詳細」画面に表示されるソースタイプ・カテゴリ・有効状態の画面を取得する</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11" ht="100" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>RDSイベントサブスクリプション(クラスター)</t>
@@ -3514,14 +3706,15 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>イベントサブスクリプションが設計通りになっていること
-・ソースタイプ: クラスター
-・イベントカテゴリ: すべて
-・有効: ON</t>
+・ソースタイプ: クラスター・イベントカテゴリ: すべて・有効: ON</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でRDS &gt; イベントサブスクリプションを選択し、設定を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「RDS」&gt;「イベントサブスクリプション」を選択
+②対象のサブスクリプション(クラスター)をクリック
+③「詳細」画面に表示されるソースタイプ・カテゴリ・有効状態の画面を取得する</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -3542,7 +3735,7 @@
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3568,7 +3761,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="100" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>シークレット基本設定</t>
@@ -3576,19 +3769,21 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>シークレット(RDSパスワードローテーション用)が要求仕様通りの設定で構築されていること
-・名前タグ(xxxxx-prd-secret)
-・PasswordRotation/Days: rate(30 days)</t>
+          <t>シークレット(RDSパスワードローテーション用)が設計通りの設定で構築されていること
+・名前タグ・PasswordRotation/Days: rate(30 days)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSecrets Manager &gt; シークレットを選択し、詳細を確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Secrets Manager」&gt;「シークレット」を選択
+②対象のシークレットをクリック
+③「概要」セクションに表示されるシークレット名・ARN等の画面を取得する</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3" ht="100" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>シークレットローテーション設定</t>
@@ -3602,7 +3797,10 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSecrets Manager &gt; シークレット &gt; ローテーションタブを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Secrets Manager」&gt;「シークレット」を選択
+②対象のシークレットをクリック
+③「ローテーション設定」セクションに表示されるローテーション有効状態・間隔の画面を取得する</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -3611,7 +3809,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>シークレットとRDSの連携確認</t>
@@ -3624,7 +3822,10 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>AWSコンソール上でSecrets Manager &gt; シークレット &gt; 概要タブでRDS DBインスタンスの関連付けを確認</t>
+          <t>AWSコンソール上で
+①左メニュー「Secrets Manager」&gt;「シークレット」を選択
+②対象のシークレットをクリック
+③「概要」セクション内「シークレットの値」または「タグ」に表示されるRDSインスタンス関連付けの画面を取得する</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
